--- a/src/JinZhaoYi.GasQcDataLoader/templates/COA(大卡).xlsx
+++ b/src/JinZhaoYi.GasQcDataLoader/templates/COA(大卡).xlsx
@@ -1838,7 +1838,7 @@
       <c r="A11" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="7" t="s">
         <v>103</v>
       </c>
       <c r="C11" s="45"/>
